--- a/프로젝트 설계.xlsx
+++ b/프로젝트 설계.xlsx
@@ -5,15 +5,16 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PRO\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PRO\Desktop\GitDesktop\BongTMI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25C37808-366C-45B7-A6BC-6D61D591FF71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD683EC4-9BE9-46BA-84E1-4FB51CBEE3A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{22406B6D-1F8B-4CDA-924C-3ADA33D22E65}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{22406B6D-1F8B-4CDA-924C-3ADA33D22E65}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1 (2)" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="80">
   <si>
     <t>components</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -210,10 +211,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>18버전</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>프론트</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -295,6 +292,58 @@
   </si>
   <si>
     <t>config</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>봉사 추천 / 봉사 검색 / 봉사 등록 / 봉사 소식 / 내 정보</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>단톡방 / 알람</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Yes, No, Detail</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>비회원 막고, 신청시 단톡방으로 리디렉트</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>검색(공고만) - 기관유무, 오늘자등록, 모집기간, 지역.. 등</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>신청한 공고 / 좋아요한 공고 / 작성한 공고 / 작성한 피드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Detail</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>알잘딱</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이메일 인증(파이어베이스)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(정식 신청)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>누가 봉사 신청했는지, 신청한or좋아요 봉사 마감 알림</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>소식(공지겸 훈훈한 뉴스 스크랩), 후기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>통계, AI가 너를 어떻게 분석하고 있는지</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -302,7 +351,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -344,13 +393,60 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C5700"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -362,12 +458,21 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -380,8 +485,23 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="2">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="4">
+    <cellStyle name="나쁨" xfId="2" builtinId="27"/>
+    <cellStyle name="보통" xfId="3" builtinId="28"/>
+    <cellStyle name="좋음" xfId="1" builtinId="26"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -694,294 +814,339 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D58C89D2-967B-4DA1-9D00-5CB04390D60F}">
-  <dimension ref="A1:P43"/>
+  <dimension ref="A1:R43"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.125" customWidth="1"/>
     <col min="2" max="2" width="21.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="31.5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" ht="31.5" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="J1" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="B1" t="s">
-        <v>44</v>
-      </c>
-      <c r="H1" s="2" t="s">
+      <c r="R1" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="P1" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>39</v>
       </c>
-      <c r="H2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="J2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="H3" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="J3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="I4" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="K4" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B5" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="J5" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="L5" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>43</v>
       </c>
-      <c r="J6" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="L6" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B7" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="J7" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="L7" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B8" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="J8" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="L8" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B9" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="I9" t="s">
+      <c r="K9" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B10" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="J10" s="1" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="L10" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="J11" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="L11" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B12" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="J12" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C12" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="L12" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B13" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="J13" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C13" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="L13" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="I14" t="s">
+      <c r="K14" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B15" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J15" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C15" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="L15" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B16" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J16" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C16" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="L16" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="17" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B17" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="J17" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C17" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="L17" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="18" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B18" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="J18" s="1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C18" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="L18" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="19" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B19" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="I19" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C19" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="K19" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="20" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B20" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C21" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="J21" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="E21" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="L21" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="22" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B22" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="I22" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K22" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="23" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C23" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C25" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B26" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C27" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="H27" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="E27" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="J27" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="28" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C28" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="I28" s="1" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="E28" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="K28" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="29" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B29" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C30" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:12" x14ac:dyDescent="0.3">
       <c r="D31" s="1" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="F31" s="4" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="32" spans="2:12" x14ac:dyDescent="0.3">
       <c r="D32" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="F32" s="4" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="D33" s="1" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="F33" s="4" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="C34" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="D35" s="1" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="F35" s="4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="D36" s="1" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="F36" s="4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="C37" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B38" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="C39" s="1" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D39" s="4" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B41" s="1" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
         <v>3</v>
       </c>
@@ -989,8 +1154,320 @@
         <v>4</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14FB0B89-65AE-4EFD-97E3-89D62C98B1AB}">
+  <dimension ref="A1:R34"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="14.125" customWidth="1"/>
+    <col min="2" max="2" width="21.125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" ht="31.5" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="R1" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="J2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B3" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="J3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B4" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="K4" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B6" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B7" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B8" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B9" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="K9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B10" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="L10" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B11" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L11" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="C12" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="L12" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B13" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="L13" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="C14" t="s">
+        <v>12</v>
+      </c>
+      <c r="K14" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B15" t="s">
+        <v>13</v>
+      </c>
+      <c r="L15" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="C16" t="s">
+        <v>12</v>
+      </c>
+      <c r="L16" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B17" t="s">
+        <v>15</v>
+      </c>
+      <c r="L17" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="C18" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="L18" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="C19" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="K19" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B20" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="C21" t="s">
+        <v>25</v>
+      </c>
+      <c r="L21" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="D22" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="K22" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="D23" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="D24" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="C25" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="D26" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="D27" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="J27" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="C28" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="K28" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B29" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="C30" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A31" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B32" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A33" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B33" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A34" s="1" t="s">
         <v>5</v>
       </c>
     </row>

--- a/프로젝트 설계.xlsx
+++ b/프로젝트 설계.xlsx
@@ -1,22 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PRO\Desktop\GitDesktop\BongTMI\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SSAFY\Desktop\GitDesktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD683EC4-9BE9-46BA-84E1-4FB51CBEE3A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{22406B6D-1F8B-4CDA-924C-3ADA33D22E65}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet1 (2)" sheetId="2" r:id="rId2"/>
+    <sheet name="프로젝트 구조" sheetId="2" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -35,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="107">
   <si>
     <t>components</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -53,10 +51,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>라우팅용</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>main.tsx</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -77,22 +71,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Swipe</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Search</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>AddBong</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Feed</t>
   </si>
   <si>
@@ -116,10 +94,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>MyPage</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>UserLogin.tsx</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -143,18 +117,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>etc</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Alarm.tsx</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Oauth</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>KakaoCallback.tsx</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -171,46 +137,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>API.tsx</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BongAPI.tsx</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>UserAPI.tsx</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>FeedAPI.tsx</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>GlobalStyle.ts</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>stores</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BongStore.ts</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>UserStore.ts</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>FeedStore.ts</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>apis</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>프론트</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -335,22 +265,198 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>누가 봉사 신청했는지, 신청한or좋아요 봉사 마감 알림</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>소식(공지겸 훈훈한 뉴스 스크랩), 후기</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>통계, AI가 너를 어떻게 분석하고 있는지</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bong</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>라우팅</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>봉사 신청자 알림, 신청한or좋아요 봉사 마감 알림</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bong</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1365 API 기준)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>User</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(OAuth 기준)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Feed</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bong.sql</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Feed.sql</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>제목</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>작성자</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>작성시간</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>내용</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>좋아요</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>조회수</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Comment</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bong, Feed 고유번호(PK) 따라감</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>User.sql</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GLOBAL.sql</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(DB CRUD)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bong progrmRegistNo 외래키</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BongID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">0,1,2? 각 싫어요/좋아요/신청하기 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>선택여부</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FeedID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LikeBong</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LikeFeed</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Chat</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WebSocketConfig.java</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Chat.sql</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ChatList.java</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ChatRoom.java</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ChatList.tsx</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ChatRoom.tsx</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ChatRoom</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Chat</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ChatID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Chat PK 외래키</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>작성자</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>config.tsx</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>temp</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ResetStorage.tsx</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OAuth</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -426,7 +532,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -446,6 +552,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -472,7 +584,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -495,6 +607,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -813,662 +928,433 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D58C89D2-967B-4DA1-9D00-5CB04390D60F}">
-  <dimension ref="A1:R43"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:T33"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="14.125" customWidth="1"/>
-    <col min="2" max="2" width="21.125" customWidth="1"/>
+    <col min="1" max="1" width="14.09765625" customWidth="1"/>
+    <col min="2" max="2" width="21.09765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="31.5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" ht="30" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="R1" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>39</v>
-      </c>
-      <c r="J2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="B3" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="J3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="B4" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="K4" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="B5" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="L5" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>43</v>
-      </c>
-      <c r="L6" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="B7" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="L7" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="B8" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="L8" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="B9" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="K9" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="B10" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="L10" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A11" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="L11" s="1" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="B12" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="L12" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="B13" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="L13" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A14" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="K14" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="B15" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="L15" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="B16" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="L16" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B17" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="L17" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B18" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="L18" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="19" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B19" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="K19" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="20" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B20" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="21" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="C21" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E21" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="L21" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B22" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="K22" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="C23" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B24" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="25" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="C25" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B26" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="27" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="C27" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E27" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="J27" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="28" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="C28" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E28" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="K28" s="1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="29" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B29" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="30" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="C30" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="31" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="D31" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F31" s="4" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="32" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="D32" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F32" s="4" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="D33" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F33" s="4" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="C34" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q1" s="2" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="D35" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F35" s="4" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="D36" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="F36" s="4" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="C37" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B38" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="C39" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D39" s="4" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B41" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B42" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A43" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14FB0B89-65AE-4EFD-97E3-89D62C98B1AB}">
-  <dimension ref="A1:R34"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="14.125" customWidth="1"/>
-    <col min="2" max="2" width="21.125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:18" ht="31.5" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="R1" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="J2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+        <v>30</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.4">
       <c r="B3" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="K3" t="s">
         <v>32</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="J3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="R3" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.4">
       <c r="B4" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="L4" t="s">
         <v>33</v>
       </c>
-      <c r="C4" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="K4" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="Q4" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A5" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="L5" s="1" t="s">
+      <c r="M5" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="R5" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.4">
+      <c r="B6" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="S6" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.4">
+      <c r="B7" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.4">
+      <c r="B8" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="4" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="B6" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" s="4" t="s">
+      <c r="M8" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="R8" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="L6" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="B7" s="6" t="s">
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.4">
+      <c r="B9" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="L9" t="s">
+        <v>9</v>
+      </c>
+      <c r="S9" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.4">
+      <c r="B10" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="L7" s="1" t="s">
+      <c r="C10" s="4" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="B8" s="6" t="s">
+      <c r="M10" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="S10" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.4">
+      <c r="B11" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="M11" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="S11" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.4">
+      <c r="C12" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="M12" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="S12" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.4">
+      <c r="B13" s="3"/>
+      <c r="C13" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="M13" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="S13" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.4">
+      <c r="C14" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="L14" t="s">
+        <v>18</v>
+      </c>
+      <c r="S14" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.4">
+      <c r="C15" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="M15" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="R15" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.4">
+      <c r="B16" t="s">
+        <v>10</v>
+      </c>
+      <c r="M16" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="S16" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="C17" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="M17" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="C18" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="M18" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="R18" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="B19" t="s">
+        <v>19</v>
+      </c>
+      <c r="L19" t="s">
+        <v>91</v>
+      </c>
+      <c r="S19" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="C20" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="M20" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="R20" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="C21" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="L8" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="B9" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="K9" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="B10" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="L10" s="1" t="s">
+      <c r="E21" s="4" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="B11" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="L11" s="1" t="s">
+      <c r="M21" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="S21" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="C22" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E22" s="4" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="C12" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="L12" s="1" t="s">
+      <c r="M22" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="S22" t="s">
+        <v>85</v>
+      </c>
+      <c r="T22" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="C23" t="s">
+        <v>106</v>
+      </c>
+      <c r="L23" t="s">
+        <v>49</v>
+      </c>
+      <c r="S23" t="s">
+        <v>87</v>
+      </c>
+      <c r="T23" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="24" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="D24" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F24" s="4" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="B13" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="L13" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="C14" t="s">
-        <v>12</v>
-      </c>
-      <c r="K14" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="B15" t="s">
-        <v>13</v>
-      </c>
-      <c r="L15" s="1" t="s">
+      <c r="M24" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="R24" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="25" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="D25" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="L25" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="S25" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="26" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="C26" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D26" s="4" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="C16" t="s">
-        <v>12</v>
-      </c>
-      <c r="L16" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B17" t="s">
-        <v>15</v>
-      </c>
-      <c r="L17" s="1" t="s">
+      <c r="J26" t="s">
+        <v>31</v>
+      </c>
+      <c r="S26" t="s">
+        <v>88</v>
+      </c>
+      <c r="T26" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="27" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="A27" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="K27" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="S27" t="s">
+        <v>87</v>
+      </c>
+      <c r="T27" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="28" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="B28" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="29" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="A29" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="R29" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="30" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="B30" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="S30" t="s">
+        <v>100</v>
+      </c>
+      <c r="T30" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="31" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="A31" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B31" s="4" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="C18" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E18" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="L18" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="C19" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E19" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="K19" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B20" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="C21" t="s">
-        <v>25</v>
-      </c>
-      <c r="L21" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="D22" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F22" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="K22" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="D23" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F23" s="4" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="D24" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F24" s="4" t="s">
+      <c r="R31" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="32" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="A32" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="S32" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19" x14ac:dyDescent="0.4">
+      <c r="A33" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="S33" t="s">
         <v>75</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="C25" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="D26" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F26" s="4" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="D27" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="F27" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="J27" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="C28" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D28" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="K28" s="1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B29" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="C30" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D30" s="4" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A31" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B32" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A33" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B33" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A34" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
   </sheetData>
